--- a/AAII_Financials/Quarterly/AJG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AJG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>AJG</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3857000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4630000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3464500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3158300</v>
       </c>
-      <c r="G8" s="3">
-        <v>2945400</v>
-      </c>
       <c r="H8" s="3">
+        <v>2946000</v>
+      </c>
+      <c r="I8" s="3">
         <v>3441000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2534700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2631200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2637400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3124700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2274400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2352000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2326300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2606500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2028300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2044000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2043000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2435300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1972700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2138200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1933500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2165000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1703600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1849100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1584000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1866900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1721400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1825200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1657800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1990600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1657400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1778500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1660400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1837700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1519400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1593700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1489500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1646400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1385000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1482300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2174000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2398000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2184100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1828300</v>
       </c>
-      <c r="G9" s="3">
-        <v>1691800</v>
-      </c>
       <c r="H9" s="3">
+        <v>1693000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1819000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1619000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1516200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1526100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1639700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1343700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1372900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1333700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1355500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1152000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1159500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1159700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1290900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1249700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1386700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1228500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1302900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1123000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1214200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>988000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1119000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1176100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1270800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1131300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1252700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1228400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1311800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1201900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1241800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1142600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1165700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1099200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1111800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>988700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1076300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1683000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2232000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1280400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1330000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1253600</v>
-      </c>
       <c r="H10" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1622000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>915700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1115000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1111300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1485000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>930700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>979100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>992600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1251000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>876300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>884500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>883300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1144400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>723000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>751500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>705000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>862100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>580600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>634900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>596000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>747900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>545300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>554400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>526500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>737900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>429000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>466700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>458500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>595900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>376800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>428000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>390300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>534600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>396300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>406000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,8 +1249,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1358,8 +1372,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,89 +1497,92 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>255000</v>
+      </c>
+      <c r="E14" s="3">
         <v>200000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>142200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>203000</v>
       </c>
-      <c r="G14" s="3">
-        <v>129700</v>
-      </c>
       <c r="H14" s="3">
+        <v>130000</v>
+      </c>
+      <c r="I14" s="3">
         <v>174000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>131700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>153200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>99800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>453800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>81800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>121200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>129500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>123300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>70500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>51600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>59000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>48600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>29700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>18400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>24300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>25800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>27100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2900</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1578,8 +1598,8 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1602,130 +1622,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>337000</v>
+      </c>
+      <c r="E15" s="3">
         <v>338000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>338500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>273900</v>
       </c>
-      <c r="G15" s="3">
-        <v>230800</v>
-      </c>
       <c r="H15" s="3">
+        <v>230000</v>
+      </c>
+      <c r="I15" s="3">
         <v>214000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>214100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>204600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>197600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>207700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>189500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>171600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>175700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>159400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>154000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>145500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>140300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>159800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>146500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>131300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>145200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>143300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>133500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>133900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>122600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>172400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>129600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>119300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>115000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>110500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>109800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>106200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>104200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>98800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>96600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>100100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>95300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>93800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>89300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3118000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3315000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3102900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2614700</v>
       </c>
-      <c r="G17" s="3">
-        <v>2418200</v>
-      </c>
       <c r="H17" s="3">
+        <v>2418000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2483000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2233100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2138600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2122900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2253400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1943300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1934900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1910500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1803300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1842300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1664600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1626100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1833700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1799700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1849500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1653900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1704400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1526500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1594100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1357200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1448000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1589300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1663800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1507400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1628600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1577700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1651500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1522900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1564100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1459000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1485400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1403800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1416900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1287900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1358900</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>739000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1315000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>361600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>543600</v>
       </c>
-      <c r="G18" s="3">
-        <v>527200</v>
-      </c>
       <c r="H18" s="3">
+        <v>528000</v>
+      </c>
+      <c r="I18" s="3">
         <v>958000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>301600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>492600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>514500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>871300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>331100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>417100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>415800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>803200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>186000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>379400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>416900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>601600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>173000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>288700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>279600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>460600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>177100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>255000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>226800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>418900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>132100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>161400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>150400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>362000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>79700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>127000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>137500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>273600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>60400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>108300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>85700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>229500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>97100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,8 +2086,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2097,8 +2131,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2110,32 +2144,32 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -2175,496 +2209,511 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1076000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1653000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>700100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>817500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>758000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1172000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>515700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>697200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>712100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1079000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>520600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>588700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>591500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>962600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>340000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>524900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>557200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>761400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>321000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>423000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>423700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>599800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>315000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>391500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>344300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>578900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>261700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>280700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>265400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>472500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>189500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>233200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>241700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>372400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>157000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>208400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>181000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>323300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>186400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>212300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E22" s="3">
         <v>158000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>161200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>160800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>158600</v>
       </c>
       <c r="H22" s="3">
         <v>158000</v>
       </c>
       <c r="I22" s="3">
+        <v>158000</v>
+      </c>
+      <c r="J22" s="3">
         <v>101600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>92900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>94300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>92200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>78200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>72800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>77800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>67900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>64000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>64400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>64600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>63900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>61500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>60300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>56200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>48100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>47800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>48100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>50000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>50500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>48100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>44900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>40200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>36500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>36700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>33900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>31300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>31200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>31400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>31600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>29900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>28300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1043000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>180000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>346900</v>
       </c>
-      <c r="G23" s="3">
-        <v>471400</v>
-      </c>
       <c r="H23" s="3">
+        <v>473000</v>
+      </c>
+      <c r="I23" s="3">
         <v>873000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>333400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>403300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>365600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>772700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-82200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>364100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>297400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>605800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>122000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>315000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>352300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>537700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>113000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>231400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>222300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>408400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>133700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>209500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>171700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>356000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>84000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>114800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>105500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>321800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>43200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>90300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>103600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>242300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>29200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>76900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>54100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>199600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>68800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>94900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E24" s="3">
         <v>220000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>25700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>73300</v>
       </c>
-      <c r="G24" s="3">
-        <v>105200</v>
-      </c>
       <c r="H24" s="3">
+        <v>105000</v>
+      </c>
+      <c r="I24" s="3">
         <v>164000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>74600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>89200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>80200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>160000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-42600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>80900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>61600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>119200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-13500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>58700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>67200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>98600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-7200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>20500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>11500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-35500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-23600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-42200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-81400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-49200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-25000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-49800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-86100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-41200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-24200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-42400</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-32200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-35500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E26" s="3">
         <v>823000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>154300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>273600</v>
       </c>
-      <c r="G26" s="3">
-        <v>366200</v>
-      </c>
       <c r="H26" s="3">
+        <v>368000</v>
+      </c>
+      <c r="I26" s="3">
         <v>709000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>258800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>314100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>285400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>612700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-39600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>283200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>235800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>486600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>135500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>256300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>285100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>439100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>120900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>238600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>201800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>393700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>153100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>187800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>161800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>355400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>72500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>150300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>129100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>364000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>124600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>139500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>128600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>292100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>115300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>118100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>78300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>242000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>101000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>130400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E27" s="3">
         <v>822000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>151100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>272700</v>
       </c>
-      <c r="G27" s="3">
-        <v>365800</v>
-      </c>
       <c r="H27" s="3">
+        <v>368000</v>
+      </c>
+      <c r="I27" s="3">
         <v>704000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>258600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>312600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>283400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>608400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-32200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>280700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>234500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>486500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>135500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>255800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>284200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>438700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>109400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>225100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>190200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>382100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>142200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>176600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>153700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>346300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>65400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>139300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>117800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>346400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>114100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>128700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>119800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>279800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>108300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>111000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>70000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>228800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>95100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>122800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3213,8 +3274,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -3231,36 +3292,36 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>33100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-12300</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>3200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-4900</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-6100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-36800</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,8 +3584,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3561,8 +3631,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3574,32 +3644,32 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12400</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3639,130 +3709,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E33" s="3">
         <v>822000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>151100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>272700</v>
       </c>
-      <c r="G33" s="3">
-        <v>365800</v>
-      </c>
       <c r="H33" s="3">
+        <v>368000</v>
+      </c>
+      <c r="I33" s="3">
         <v>704000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>258600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>312600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>283400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>608400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-32200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>280700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>234500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>486500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>135500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>255800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>284200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>438700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>109400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>225100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>190200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>382100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>142200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>176600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>153700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>346300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>98500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>126100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>110100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>334100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>117300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>127600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>114900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>273700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>71500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>111000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>70000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>228800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>95100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>122800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E35" s="3">
         <v>822000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>151100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>272700</v>
       </c>
-      <c r="G35" s="3">
-        <v>365800</v>
-      </c>
       <c r="H35" s="3">
+        <v>368000</v>
+      </c>
+      <c r="I35" s="3">
         <v>704000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>258600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>312600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>283400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>608400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-32200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>280700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>234500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>486500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>135500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>255800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>284200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>438700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>109400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>225100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>190200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>382100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>142200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>176600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>153700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>346300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>98500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>126100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>110100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>334100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>117300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>127600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>114900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>273700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>71500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>111000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>70000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>228800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>95100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>122800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,130 +4306,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1386000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1413000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1396000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1399300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14299500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16691800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14987000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2022400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1415300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1762600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>971500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1027500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>952300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1549900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>738400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>553700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>523600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>528600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>402600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2735100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3204100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>526300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>664600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>629900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>349700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>352800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>604800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>578900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>512300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>871500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>607200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>605000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>652200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>697900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>681200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>564900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>587800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>564000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>545500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>531800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4351,17 +4441,17 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>7000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2700</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -4378,14 +4468,14 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>88500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>57700</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4464,130 +4554,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6076000</v>
+      </c>
+      <c r="E43" s="3">
         <v>5960000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5175000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5426300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4739200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4520200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3896000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3988800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4178300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4148700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3786600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3769300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3716300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3526500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20439800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18259600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>19687600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22617700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12902700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8923000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9351500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9122400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7335800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7561700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7593500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7730200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6279800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6561800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6834400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6978600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5682100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5723600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5924900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>6329600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4872900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2817900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2959600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2579300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2400100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2206900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4630,8 +4726,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4708,252 +4804,261 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37990000</v>
+      </c>
+      <c r="E45" s="3">
         <v>34646000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27778000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36180700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38796700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32227100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25230000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31271500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37719900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35568200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27358000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31052400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32119400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23701600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23599300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4983300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4533200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4373000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4365100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3480200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3383700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3018800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3123800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3008700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2817200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2444200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2232900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2187900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2200700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1819400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1829400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1755400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1787900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1505800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1715300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1704600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1559800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1339900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1470500</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1475000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45452000</v>
+      </c>
+      <c r="E46" s="3">
         <v>42019000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>34356000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43007800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>57838100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>53439100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>44113000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>37282700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43313500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>41479500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32116100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35937700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>36845700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>28778000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22285200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23796600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24744400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>27519300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17670400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15138300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15939300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12667500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>11124200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11200300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>10760400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10527200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9117500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9328600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9547400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9669500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8118700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8084000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8365000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8533300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7269400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5087400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>5107200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4483200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4416100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4213700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4987,51 +5092,51 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>29600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>45300</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V47" s="3">
         <v>5500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>17100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>20800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>22400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>25900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>30400</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
@@ -5047,8 +5152,8 @@
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH47" s="3">
-        <v>0</v>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
@@ -5074,252 +5179,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1343000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1347000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1387000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1433300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1147400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1024600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1028000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1034800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1037600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1090700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1126700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1016000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1017500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>936400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>922900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>909200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>932800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>887300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>859400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>784800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>813200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>819400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>824600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>805100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>823600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>829100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>860900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>843300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>826400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>819000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>436900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>429300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>427600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>424200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>412200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>413400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>387600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>375500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>377600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>213900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33238000</v>
+      </c>
+      <c r="E49" s="3">
         <v>33324000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33277000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32967700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18871900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17246900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16800000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16546600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16304900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16153800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16108900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14054000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14234100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13107300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>12861500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11889600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>12227300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>12605300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12620200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8966500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9077600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8989700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8526900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8027200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7982400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7802000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7937200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7388300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7250700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6642300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6398600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6273400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>6134900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5875900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5809400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5831600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5651600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5579000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5395100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5392500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1732000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1568000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1602000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1629700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1573600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1494900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1355000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1361800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1311600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1197000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1131800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1056300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1105800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>983300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2288800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2072400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2085900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2149600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2189500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2012100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1970000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1917100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1833300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1756400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1709400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1678200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1719200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1613600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1575800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1500600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1379800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1328000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1303000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1294100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1418700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1423200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1342900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1300800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1380200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>81808000</v>
+      </c>
+      <c r="E54" s="3">
         <v>78301000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70665000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79067900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>80122600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74095700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64255000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>57242700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>63007700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>60975900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>51615800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>53203900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>54365200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>45094400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>38358400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>38667800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>39990400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43161500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33345000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26915800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>27817200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24414500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22331400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21814900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21306200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20836500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19634800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19173800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19200300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>18631400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16334000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16114700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16230500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>16127500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>14909700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>12810400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>12569600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>11780600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>11489600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>11200300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,8 +6146,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6060,696 +6191,714 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3">
         <v>18698200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19273400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20381200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>23175400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13845600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9161700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9716700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9205000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7784600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7952900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7950500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7778700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6348500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6573900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6873800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6741400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5740200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5693600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5982700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6071300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4986000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3508500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3546400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3028200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2996100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2866900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1654000</v>
+      </c>
+      <c r="E58" s="3">
         <v>796000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1005000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1026800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>814000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>667800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>425000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>462000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>487800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>292500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>964700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>704000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1111200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>834800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>551900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>685400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>887200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>423400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>473400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>434100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>366100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>151300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>278600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>318000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>328600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>577600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>790600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>660100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>562300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>494800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>519000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>389300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>346100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>481000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>441100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>281400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>468000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>799400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>703600</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>741100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37971000</v>
+      </c>
+      <c r="E59" s="3">
         <v>34682000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27637000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36238800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>38922200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>32399500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25251000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31517800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38016600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>35880000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27556500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31349900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32422800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24042300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20786700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2497800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2236300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2546000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2416000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2064000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1938500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2159700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2071800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1846300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1584900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1481500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1781900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1676900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1496400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1401700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1434400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1339700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1239800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1190100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1434300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>915300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>843600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>957100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>912000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>790900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43173000</v>
+      </c>
+      <c r="E60" s="3">
         <v>39529000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32519000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>40760100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>42539600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37036000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29260000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35199500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41609600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39636500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31064700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34473900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35588800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27095700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21338600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22456600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>23504700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26144800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16735000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11659800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12021300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11516000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10135000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10117200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9864000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9837800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8921000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8910900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8932500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8637900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7693600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7422600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7568600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7742400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6730200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4705200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4858000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4784700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4611700</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4398900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12452000</v>
+      </c>
+      <c r="E61" s="3">
         <v>12576000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12619000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12678000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12499900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12755100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13060000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8118100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8126100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8327600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7358200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6345300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6354900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6333500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5562800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5562200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5561500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5760900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5810200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5072400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5712200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4366300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4266000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4265700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4315400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4315100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3816100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3815800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3815600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3690300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3091400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3141200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3141000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2792100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2691900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2741700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2644800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2144700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2144600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2044600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2259000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2217000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1706000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2269100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1960000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1884600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1582000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1650200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1606900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1602900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2186500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1813100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1919800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1744900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2266800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2019900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2062400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2212700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2239700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1713500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1729700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1752700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1697700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1613800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1592300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1613500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1682200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1535100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1504400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1345000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>979300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>938200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1007800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1008500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1187900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1191300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1156800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1123900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1077500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1015600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58061000</v>
+      </c>
+      <c r="E66" s="3">
         <v>54499000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47318000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55831000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57066300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51742000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>44075000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45033100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51408400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>49631700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40800500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>42693900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>43925200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35236100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29214800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30094000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31181700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34172100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>24836600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18495600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19504500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17683400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16145200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16043200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15817600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15807000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14479300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14330500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14320900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13751100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11835100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11570200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11786900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11612900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10674100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8700400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>8724900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8118100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7893000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7513800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6588000</v>
+      </c>
+      <c r="E72" s="3">
         <v>6446000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5806000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5824700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5720700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5522900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4986000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4860600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4681200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4529300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4052900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4205700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4045100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3930200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3562200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3536200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3388700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3213000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2882300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2873800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2749100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2658900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2371700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2317300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2228300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2161400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1901300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1884200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1839300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1810200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1558600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1517600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1466000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1426700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1221800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1062100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1002900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>901800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>916400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>889800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23717000</v>
+      </c>
+      <c r="E76" s="3">
         <v>23775000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23321000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23205800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23023100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22320100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20154000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12184000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11572500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11300800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10775300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10463500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10395700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9817800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9143600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8573800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8808700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8989400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8508400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8420200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8312700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6731100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6186200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5771700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5488600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5029500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5155500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4843300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4879400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4880300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4498900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4544500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4443600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4514600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4235600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4110000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3844700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3662500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3596600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3686500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E81" s="3">
         <v>822000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>151100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>272700</v>
       </c>
-      <c r="G81" s="3">
-        <v>365800</v>
-      </c>
       <c r="H81" s="3">
+        <v>368000</v>
+      </c>
+      <c r="I81" s="3">
         <v>704000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>258600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>312600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>283400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>608400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-32200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>280700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>234500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>486500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>135500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>255800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>284200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>438700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>109400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>225100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>190200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>382100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>142200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>176600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>153700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>346300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>98500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>126100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>110100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>334100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>117300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>127600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>114900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>273700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>71500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>111000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>70000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>228800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>95100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>122800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E83" s="3">
         <v>45000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>46500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>40800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>45400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>43700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>43000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>40800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>40000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>35200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>154000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>145500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>140300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>159800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>146500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>131300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>145200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>143300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>133500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>133900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>122600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>172400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>129600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>119300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>115000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>110500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>109800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>106200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>104200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>98800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>96600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>100100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>95300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>93800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>89300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E89" s="3">
         <v>957000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>753000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>731300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-426100</v>
-      </c>
       <c r="H89" s="3">
+        <v>-424000</v>
+      </c>
+      <c r="I89" s="3">
         <v>872000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>739400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>934800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>119500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>789300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>693600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>897200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>428500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>200400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1156700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>333700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>434600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>493800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>521400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>402600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>286300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>419500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>585400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>693600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>108600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>350100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>349500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>515800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-96200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>260500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>191300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>530900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-217600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>261000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>332300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>91200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>169700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>261200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>243400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-39600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-39400</v>
-      </c>
       <c r="H91" s="3">
+        <v>-40000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-28000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-29700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-46000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-58800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-49200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-53400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-37700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-25400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-44000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-32000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-19800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-29300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-33600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-35400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-36300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-58600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-158000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-71400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-353000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-238000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-471600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13783900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1345100</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1346000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-275000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-857000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-230400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-307700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-191900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-327400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-808500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-256600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-442700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-192200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-275600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-94300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2710000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-119600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-251800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-350300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-254000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-34800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-105000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-396200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-247600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-591500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-141300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-256500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-208100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-358800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-86900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-108800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-118800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-113200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-170200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-184500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-91500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,130 +10456,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E96" s="3">
         <v>180000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>167500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>166900</v>
       </c>
-      <c r="G96" s="3">
-        <v>166600</v>
-      </c>
       <c r="H96" s="3">
+        <v>167000</v>
+      </c>
+      <c r="I96" s="3">
         <v>166000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>131400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>131600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>131300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>130700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>119100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>118600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>118500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>117400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-108000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-107500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-107300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-106700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-99800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-89800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-105000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-97400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-87300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-86600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-86100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-87400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-81300</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-80100</v>
       </c>
       <c r="AE96" s="3">
         <v>-80100</v>
       </c>
       <c r="AF96" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-79600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-75600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-75300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-74800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-76100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-71100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-70200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-71400</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-67900</v>
       </c>
       <c r="AP96" s="3">
         <v>-67900</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-67900</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1251000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-723000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-172900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>568600</v>
       </c>
-      <c r="G100" s="3">
-        <v>210300</v>
-      </c>
       <c r="H100" s="3">
+        <v>210000</v>
+      </c>
+      <c r="I100" s="3">
         <v>1107000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12499700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>611500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-53800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>982100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-668500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1602200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>958100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>482300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-269200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-18200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>17700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>682500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-662800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2782500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-118100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-123900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-128700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>147900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>9700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>112700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>507400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>5200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-44800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>132100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>69500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-165600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>99100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>19900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>2300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-14500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E101" s="3">
         <v>67000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-208800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>141300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-54500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-17300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-58100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>45100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>182800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-208200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-106900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>32400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>182800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-208200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-106900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>32400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-81400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-33200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>13800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>36300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>112500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>38400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>111100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-142200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>53000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-49800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>34100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-32900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-22600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-68200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>38700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-26500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>63700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>15600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>19200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-15100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>851000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-56000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>198300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12466200</v>
       </c>
-      <c r="G102" s="3">
-        <v>-1433100</v>
-      </c>
       <c r="H102" s="3">
+        <v>-1432000</v>
+      </c>
+      <c r="I102" s="3">
         <v>1771000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12173300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1457200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-243000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>537500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-242100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-156800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>851200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1126800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-312600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>487100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>151000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>172400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1546000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-362700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3014100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-213400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>99500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>472100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>369500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>16600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>60700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>5800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>304000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-23700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-84200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>236000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-196300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>124500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>111600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>112800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>18500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>13700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>120700</v>
       </c>
     </row>
